--- a/products/wedding-command-center/Wedding_Command_Center.xlsx
+++ b/products/wedding-command-center/Wedding_Command_Center.xlsx
@@ -1430,7 +1430,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="3240000"/>
+    <ext cx="4320000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1447,12 +1447,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="3240000"/>
+    <ext cx="4320000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1471,10 +1471,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="3240000"/>
+    <ext cx="4320000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1491,12 +1491,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4680000" cy="3240000"/>
+    <ext cx="4320000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1540,12 +1540,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3240000"/>
+    <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1594,12 +1594,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2880000"/>
+    <ext cx="4320000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1616,12 +1616,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2880000"/>
+    <ext cx="4320000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1956,7 +1956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2185,8 +2185,8 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="B52" s="2" t="inlineStr">
+    <row r="56" ht="26" customHeight="1">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Wedding Command Center v1.0  ·  Edit Settings → Wedding Date · Budget · Guests  ·  Hyperlink nav chips to each sheet in Excel/Sheets</t>
         </is>
@@ -2205,7 +2205,7 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="B56:K56"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="B11:K11"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="D5" s="19" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="D6" s="22" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F7" s="18" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="D8" s="22" t="n"/>
       <c r="E8" s="22" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D9" s="19" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="D10" s="22" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D11" s="19" t="n"/>
       <c r="E11" s="19" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="D12" s="22" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D13" s="19" t="n"/>
       <c r="E13" s="19" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="F5" s="19" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="F9" s="19" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="C5" s="19" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="D5" s="32" t="n">
         <v>120</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="C6" s="22" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="D6" s="34" t="n">
         <v>180</v>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>200</v>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="C8" s="22" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>45</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>60</v>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="C10" s="22" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>45</v>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>350</v>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="C12" s="22" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D12" s="34" t="n">
         <v>220</v>
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="C6" s="22" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D6" s="34" t="n">
         <v>2400</v>
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>4200</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="C8" s="22" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>180</v>
@@ -13171,7 +13171,7 @@
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>350</v>
@@ -13199,7 +13199,7 @@
         </is>
       </c>
       <c r="C10" s="22" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>200</v>
@@ -13223,7 +13223,7 @@
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>160</v>
@@ -13247,7 +13247,7 @@
         </is>
       </c>
       <c r="C12" s="22" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D12" s="34" t="n">
         <v>250</v>
@@ -13301,7 +13301,7 @@
         </is>
       </c>
       <c r="C14" s="22" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>220</v>
@@ -14144,7 +14144,7 @@
         <v>450</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>500</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>120</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>700</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>100</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>60</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         </is>
       </c>
       <c r="E8" s="22" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
     </row>
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         </is>
       </c>
       <c r="E6" s="22" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="E7" s="19" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="E8" s="22" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         </is>
       </c>
       <c r="E9" s="19" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="E12" s="22" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="E14" s="22" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         </is>
       </c>
       <c r="E16" s="22" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="E17" s="19" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="E18" s="22" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         </is>
       </c>
       <c r="E19" s="19" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         </is>
       </c>
       <c r="E21" s="19" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>6000</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>3000</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>2000</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>2300</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>650</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>7000</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>1700</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>1500</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>1400</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>800</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>

--- a/products/wedding-command-center/Wedding_Command_Center.xlsx
+++ b/products/wedding-command-center/Wedding_Command_Center.xlsx
@@ -677,7 +677,12 @@
           </val>
         </ser>
         <dLbls>
-          <showPercent val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -926,7 +931,12 @@
           </val>
         </ser>
         <dLbls>
-          <showVal val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="1"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -1069,7 +1079,12 @@
           </val>
         </ser>
         <dLbls>
-          <showPercent val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -1324,7 +1339,12 @@
           </val>
         </ser>
         <dLbls>
-          <showVal val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="1"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>

--- a/products/wedding-command-center/Wedding_Command_Center.xlsx
+++ b/products/wedding-command-center/Wedding_Command_Center.xlsx
@@ -61,6 +61,7 @@
     <definedName name="RelationList">Settings!$H$27:$H$32</definedName>
     <definedName name="YesNoList">Settings!$I$27:$I$28</definedName>
     <definedName name="PhaseList">Settings!$J$27:$J$36</definedName>
+    <definedName name="TableList">Settings!$B$17:$B$36</definedName>
     <definedName name="TLTask">Timeline!$B$5:$B$84</definedName>
     <definedName name="TLDone">Timeline!$F$5:$F$84</definedName>
     <definedName name="ChkTask">Checklist!$B$5:$B$124</definedName>
@@ -84,6 +85,8 @@
     <definedName name="GuestInvited">Guests!$F$5:$F$204</definedName>
     <definedName name="GuestMeal">Guests!$I$5:$I$204</definedName>
     <definedName name="GuestThankYou">Guests!$L$5:$L$204</definedName>
+    <definedName name="GuestTable">Guests!$P$5:$P$204</definedName>
+    <definedName name="InspectTable">Seating!$I$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -250,7 +253,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -286,6 +289,39 @@
       <bottom style="dashed">
         <color rgb="00C9A86A"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D6D2C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D6D2C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D6D2C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D6D2C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D6D2C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D6D2C8"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="17">
@@ -339,7 +375,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -466,14 +502,27 @@
     <xf numFmtId="170" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="12">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="14">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="14">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="16">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2820,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2838,6 +2887,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -2850,7 +2900,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The master guest database — RSVP, meals, gifts, logistics.</t>
+          <t xml:space="preserve">  The master guest database — RSVP, meals, gifts, logistics. Assign each guest a table in the last column.</t>
         </is>
       </c>
     </row>
@@ -2870,6 +2920,7 @@
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -2947,6 +2998,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -3022,6 +3078,11 @@
           <t>Mother of bride</t>
         </is>
       </c>
+      <c r="P5" s="44" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
@@ -3097,6 +3158,11 @@
           <t>Father of bride</t>
         </is>
       </c>
+      <c r="P6" s="45" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
@@ -3172,6 +3238,11 @@
           <t>Best man</t>
         </is>
       </c>
+      <c r="P7" s="44" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
@@ -3247,6 +3318,11 @@
           <t>Maid of honor</t>
         </is>
       </c>
+      <c r="P8" s="45" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
@@ -3322,6 +3398,11 @@
           <t>Planner + guest</t>
         </is>
       </c>
+      <c r="P9" s="44" t="inlineStr">
+        <is>
+          <t>Table 5</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
@@ -3397,6 +3478,11 @@
           <t>Needs accessible seating</t>
         </is>
       </c>
+      <c r="P10" s="45" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -3472,6 +3558,11 @@
           <t>Family of 4, 2 kids</t>
         </is>
       </c>
+      <c r="P11" s="44" t="inlineStr">
+        <is>
+          <t>Table 7</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
@@ -3547,6 +3638,7 @@
           <t>Out of town</t>
         </is>
       </c>
+      <c r="P12" s="45" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
@@ -3622,6 +3714,11 @@
           <t>College friend</t>
         </is>
       </c>
+      <c r="P13" s="44" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -3697,6 +3794,11 @@
           <t>1 child, vegan family</t>
         </is>
       </c>
+      <c r="P14" s="45" t="inlineStr">
+        <is>
+          <t>Table 6</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
@@ -3772,6 +3874,7 @@
           <t>Work friend</t>
         </is>
       </c>
+      <c r="P15" s="44" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
@@ -3845,6 +3948,11 @@
       <c r="O16" s="21" t="inlineStr">
         <is>
           <t>Parents of groom</t>
+        </is>
+      </c>
+      <c r="P16" s="45" t="inlineStr">
+        <is>
+          <t>Table 3</t>
         </is>
       </c>
     </row>
@@ -3864,6 +3972,7 @@
       <c r="M17" s="17" t="n"/>
       <c r="N17" s="17" t="n"/>
       <c r="O17" s="18" t="n"/>
+      <c r="P17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="21" t="n"/>
@@ -3881,6 +3990,7 @@
       <c r="M18" s="20" t="n"/>
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="21" t="n"/>
+      <c r="P18" s="45" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n"/>
@@ -3898,6 +4008,7 @@
       <c r="M19" s="17" t="n"/>
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="18" t="n"/>
+      <c r="P19" s="44" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="21" t="n"/>
@@ -3915,6 +4026,7 @@
       <c r="M20" s="20" t="n"/>
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="21" t="n"/>
+      <c r="P20" s="45" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n"/>
@@ -3932,6 +4044,7 @@
       <c r="M21" s="17" t="n"/>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="18" t="n"/>
+      <c r="P21" s="44" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="n"/>
@@ -3949,6 +4062,7 @@
       <c r="M22" s="20" t="n"/>
       <c r="N22" s="20" t="n"/>
       <c r="O22" s="21" t="n"/>
+      <c r="P22" s="45" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n"/>
@@ -3966,6 +4080,7 @@
       <c r="M23" s="17" t="n"/>
       <c r="N23" s="17" t="n"/>
       <c r="O23" s="18" t="n"/>
+      <c r="P23" s="44" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="n"/>
@@ -3983,6 +4098,7 @@
       <c r="M24" s="20" t="n"/>
       <c r="N24" s="20" t="n"/>
       <c r="O24" s="21" t="n"/>
+      <c r="P24" s="45" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="n"/>
@@ -4000,6 +4116,7 @@
       <c r="M25" s="17" t="n"/>
       <c r="N25" s="17" t="n"/>
       <c r="O25" s="18" t="n"/>
+      <c r="P25" s="44" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="21" t="n"/>
@@ -4017,6 +4134,7 @@
       <c r="M26" s="20" t="n"/>
       <c r="N26" s="20" t="n"/>
       <c r="O26" s="21" t="n"/>
+      <c r="P26" s="45" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="18" t="n"/>
@@ -4034,6 +4152,7 @@
       <c r="M27" s="17" t="n"/>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="18" t="n"/>
+      <c r="P27" s="44" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="21" t="n"/>
@@ -4051,6 +4170,7 @@
       <c r="M28" s="20" t="n"/>
       <c r="N28" s="20" t="n"/>
       <c r="O28" s="21" t="n"/>
+      <c r="P28" s="45" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n"/>
@@ -4068,6 +4188,7 @@
       <c r="M29" s="17" t="n"/>
       <c r="N29" s="17" t="n"/>
       <c r="O29" s="18" t="n"/>
+      <c r="P29" s="44" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="21" t="n"/>
@@ -4085,6 +4206,7 @@
       <c r="M30" s="20" t="n"/>
       <c r="N30" s="20" t="n"/>
       <c r="O30" s="21" t="n"/>
+      <c r="P30" s="45" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n"/>
@@ -4102,6 +4224,7 @@
       <c r="M31" s="17" t="n"/>
       <c r="N31" s="17" t="n"/>
       <c r="O31" s="18" t="n"/>
+      <c r="P31" s="44" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="21" t="n"/>
@@ -4119,6 +4242,7 @@
       <c r="M32" s="20" t="n"/>
       <c r="N32" s="20" t="n"/>
       <c r="O32" s="21" t="n"/>
+      <c r="P32" s="45" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n"/>
@@ -4136,6 +4260,7 @@
       <c r="M33" s="17" t="n"/>
       <c r="N33" s="17" t="n"/>
       <c r="O33" s="18" t="n"/>
+      <c r="P33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="21" t="n"/>
@@ -4153,6 +4278,7 @@
       <c r="M34" s="20" t="n"/>
       <c r="N34" s="20" t="n"/>
       <c r="O34" s="21" t="n"/>
+      <c r="P34" s="45" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n"/>
@@ -4170,6 +4296,7 @@
       <c r="M35" s="17" t="n"/>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="18" t="n"/>
+      <c r="P35" s="44" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="21" t="n"/>
@@ -4187,6 +4314,7 @@
       <c r="M36" s="20" t="n"/>
       <c r="N36" s="20" t="n"/>
       <c r="O36" s="21" t="n"/>
+      <c r="P36" s="45" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n"/>
@@ -4204,6 +4332,7 @@
       <c r="M37" s="17" t="n"/>
       <c r="N37" s="17" t="n"/>
       <c r="O37" s="18" t="n"/>
+      <c r="P37" s="44" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="21" t="n"/>
@@ -4221,6 +4350,7 @@
       <c r="M38" s="20" t="n"/>
       <c r="N38" s="20" t="n"/>
       <c r="O38" s="21" t="n"/>
+      <c r="P38" s="45" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="n"/>
@@ -4238,6 +4368,7 @@
       <c r="M39" s="17" t="n"/>
       <c r="N39" s="17" t="n"/>
       <c r="O39" s="18" t="n"/>
+      <c r="P39" s="44" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n"/>
@@ -4255,6 +4386,7 @@
       <c r="M40" s="20" t="n"/>
       <c r="N40" s="20" t="n"/>
       <c r="O40" s="21" t="n"/>
+      <c r="P40" s="45" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="18" t="n"/>
@@ -4272,6 +4404,7 @@
       <c r="M41" s="17" t="n"/>
       <c r="N41" s="17" t="n"/>
       <c r="O41" s="18" t="n"/>
+      <c r="P41" s="44" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n"/>
@@ -4289,6 +4422,7 @@
       <c r="M42" s="20" t="n"/>
       <c r="N42" s="20" t="n"/>
       <c r="O42" s="21" t="n"/>
+      <c r="P42" s="45" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n"/>
@@ -4306,6 +4440,7 @@
       <c r="M43" s="17" t="n"/>
       <c r="N43" s="17" t="n"/>
       <c r="O43" s="18" t="n"/>
+      <c r="P43" s="44" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n"/>
@@ -4323,6 +4458,7 @@
       <c r="M44" s="20" t="n"/>
       <c r="N44" s="20" t="n"/>
       <c r="O44" s="21" t="n"/>
+      <c r="P44" s="45" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n"/>
@@ -4340,6 +4476,7 @@
       <c r="M45" s="17" t="n"/>
       <c r="N45" s="17" t="n"/>
       <c r="O45" s="18" t="n"/>
+      <c r="P45" s="44" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="21" t="n"/>
@@ -4357,6 +4494,7 @@
       <c r="M46" s="20" t="n"/>
       <c r="N46" s="20" t="n"/>
       <c r="O46" s="21" t="n"/>
+      <c r="P46" s="45" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="18" t="n"/>
@@ -4374,6 +4512,7 @@
       <c r="M47" s="17" t="n"/>
       <c r="N47" s="17" t="n"/>
       <c r="O47" s="18" t="n"/>
+      <c r="P47" s="44" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="21" t="n"/>
@@ -4391,6 +4530,7 @@
       <c r="M48" s="20" t="n"/>
       <c r="N48" s="20" t="n"/>
       <c r="O48" s="21" t="n"/>
+      <c r="P48" s="45" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="18" t="n"/>
@@ -4408,6 +4548,7 @@
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="18" t="n"/>
+      <c r="P49" s="44" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="21" t="n"/>
@@ -4425,6 +4566,7 @@
       <c r="M50" s="20" t="n"/>
       <c r="N50" s="20" t="n"/>
       <c r="O50" s="21" t="n"/>
+      <c r="P50" s="45" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="18" t="n"/>
@@ -4442,6 +4584,7 @@
       <c r="M51" s="17" t="n"/>
       <c r="N51" s="17" t="n"/>
       <c r="O51" s="18" t="n"/>
+      <c r="P51" s="44" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="21" t="n"/>
@@ -4459,6 +4602,7 @@
       <c r="M52" s="20" t="n"/>
       <c r="N52" s="20" t="n"/>
       <c r="O52" s="21" t="n"/>
+      <c r="P52" s="45" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="18" t="n"/>
@@ -4476,6 +4620,7 @@
       <c r="M53" s="17" t="n"/>
       <c r="N53" s="17" t="n"/>
       <c r="O53" s="18" t="n"/>
+      <c r="P53" s="44" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="21" t="n"/>
@@ -4493,6 +4638,7 @@
       <c r="M54" s="20" t="n"/>
       <c r="N54" s="20" t="n"/>
       <c r="O54" s="21" t="n"/>
+      <c r="P54" s="45" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="18" t="n"/>
@@ -4510,6 +4656,7 @@
       <c r="M55" s="17" t="n"/>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="18" t="n"/>
+      <c r="P55" s="44" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="21" t="n"/>
@@ -4527,6 +4674,7 @@
       <c r="M56" s="20" t="n"/>
       <c r="N56" s="20" t="n"/>
       <c r="O56" s="21" t="n"/>
+      <c r="P56" s="45" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="18" t="n"/>
@@ -4544,6 +4692,7 @@
       <c r="M57" s="17" t="n"/>
       <c r="N57" s="17" t="n"/>
       <c r="O57" s="18" t="n"/>
+      <c r="P57" s="44" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="21" t="n"/>
@@ -4561,6 +4710,7 @@
       <c r="M58" s="20" t="n"/>
       <c r="N58" s="20" t="n"/>
       <c r="O58" s="21" t="n"/>
+      <c r="P58" s="45" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="18" t="n"/>
@@ -4578,6 +4728,7 @@
       <c r="M59" s="17" t="n"/>
       <c r="N59" s="17" t="n"/>
       <c r="O59" s="18" t="n"/>
+      <c r="P59" s="44" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="21" t="n"/>
@@ -4595,6 +4746,7 @@
       <c r="M60" s="20" t="n"/>
       <c r="N60" s="20" t="n"/>
       <c r="O60" s="21" t="n"/>
+      <c r="P60" s="45" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="18" t="n"/>
@@ -4612,6 +4764,7 @@
       <c r="M61" s="17" t="n"/>
       <c r="N61" s="17" t="n"/>
       <c r="O61" s="18" t="n"/>
+      <c r="P61" s="44" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="21" t="n"/>
@@ -4629,6 +4782,7 @@
       <c r="M62" s="20" t="n"/>
       <c r="N62" s="20" t="n"/>
       <c r="O62" s="21" t="n"/>
+      <c r="P62" s="45" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="18" t="n"/>
@@ -4646,6 +4800,7 @@
       <c r="M63" s="17" t="n"/>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="18" t="n"/>
+      <c r="P63" s="44" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="21" t="n"/>
@@ -4663,6 +4818,7 @@
       <c r="M64" s="20" t="n"/>
       <c r="N64" s="20" t="n"/>
       <c r="O64" s="21" t="n"/>
+      <c r="P64" s="45" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="18" t="n"/>
@@ -4680,6 +4836,7 @@
       <c r="M65" s="17" t="n"/>
       <c r="N65" s="17" t="n"/>
       <c r="O65" s="18" t="n"/>
+      <c r="P65" s="44" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="21" t="n"/>
@@ -4697,6 +4854,7 @@
       <c r="M66" s="20" t="n"/>
       <c r="N66" s="20" t="n"/>
       <c r="O66" s="21" t="n"/>
+      <c r="P66" s="45" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="18" t="n"/>
@@ -4714,6 +4872,7 @@
       <c r="M67" s="17" t="n"/>
       <c r="N67" s="17" t="n"/>
       <c r="O67" s="18" t="n"/>
+      <c r="P67" s="44" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="21" t="n"/>
@@ -4731,6 +4890,7 @@
       <c r="M68" s="20" t="n"/>
       <c r="N68" s="20" t="n"/>
       <c r="O68" s="21" t="n"/>
+      <c r="P68" s="45" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="18" t="n"/>
@@ -4748,6 +4908,7 @@
       <c r="M69" s="17" t="n"/>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="18" t="n"/>
+      <c r="P69" s="44" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="21" t="n"/>
@@ -4765,6 +4926,7 @@
       <c r="M70" s="20" t="n"/>
       <c r="N70" s="20" t="n"/>
       <c r="O70" s="21" t="n"/>
+      <c r="P70" s="45" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="18" t="n"/>
@@ -4782,6 +4944,7 @@
       <c r="M71" s="17" t="n"/>
       <c r="N71" s="17" t="n"/>
       <c r="O71" s="18" t="n"/>
+      <c r="P71" s="44" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="21" t="n"/>
@@ -4799,6 +4962,7 @@
       <c r="M72" s="20" t="n"/>
       <c r="N72" s="20" t="n"/>
       <c r="O72" s="21" t="n"/>
+      <c r="P72" s="45" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="18" t="n"/>
@@ -4816,6 +4980,7 @@
       <c r="M73" s="17" t="n"/>
       <c r="N73" s="17" t="n"/>
       <c r="O73" s="18" t="n"/>
+      <c r="P73" s="44" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="21" t="n"/>
@@ -4833,6 +4998,7 @@
       <c r="M74" s="20" t="n"/>
       <c r="N74" s="20" t="n"/>
       <c r="O74" s="21" t="n"/>
+      <c r="P74" s="45" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="18" t="n"/>
@@ -4850,6 +5016,7 @@
       <c r="M75" s="17" t="n"/>
       <c r="N75" s="17" t="n"/>
       <c r="O75" s="18" t="n"/>
+      <c r="P75" s="44" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="21" t="n"/>
@@ -4867,6 +5034,7 @@
       <c r="M76" s="20" t="n"/>
       <c r="N76" s="20" t="n"/>
       <c r="O76" s="21" t="n"/>
+      <c r="P76" s="45" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="18" t="n"/>
@@ -4884,6 +5052,7 @@
       <c r="M77" s="17" t="n"/>
       <c r="N77" s="17" t="n"/>
       <c r="O77" s="18" t="n"/>
+      <c r="P77" s="44" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="21" t="n"/>
@@ -4901,6 +5070,7 @@
       <c r="M78" s="20" t="n"/>
       <c r="N78" s="20" t="n"/>
       <c r="O78" s="21" t="n"/>
+      <c r="P78" s="45" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="18" t="n"/>
@@ -4918,6 +5088,7 @@
       <c r="M79" s="17" t="n"/>
       <c r="N79" s="17" t="n"/>
       <c r="O79" s="18" t="n"/>
+      <c r="P79" s="44" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="21" t="n"/>
@@ -4935,6 +5106,7 @@
       <c r="M80" s="20" t="n"/>
       <c r="N80" s="20" t="n"/>
       <c r="O80" s="21" t="n"/>
+      <c r="P80" s="45" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="18" t="n"/>
@@ -4952,6 +5124,7 @@
       <c r="M81" s="17" t="n"/>
       <c r="N81" s="17" t="n"/>
       <c r="O81" s="18" t="n"/>
+      <c r="P81" s="44" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="21" t="n"/>
@@ -4969,6 +5142,7 @@
       <c r="M82" s="20" t="n"/>
       <c r="N82" s="20" t="n"/>
       <c r="O82" s="21" t="n"/>
+      <c r="P82" s="45" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="18" t="n"/>
@@ -4986,6 +5160,7 @@
       <c r="M83" s="17" t="n"/>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="18" t="n"/>
+      <c r="P83" s="44" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="21" t="n"/>
@@ -5003,6 +5178,7 @@
       <c r="M84" s="20" t="n"/>
       <c r="N84" s="20" t="n"/>
       <c r="O84" s="21" t="n"/>
+      <c r="P84" s="45" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="18" t="n"/>
@@ -5020,6 +5196,7 @@
       <c r="M85" s="17" t="n"/>
       <c r="N85" s="17" t="n"/>
       <c r="O85" s="18" t="n"/>
+      <c r="P85" s="44" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="21" t="n"/>
@@ -5037,6 +5214,7 @@
       <c r="M86" s="20" t="n"/>
       <c r="N86" s="20" t="n"/>
       <c r="O86" s="21" t="n"/>
+      <c r="P86" s="45" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="18" t="n"/>
@@ -5054,6 +5232,7 @@
       <c r="M87" s="17" t="n"/>
       <c r="N87" s="17" t="n"/>
       <c r="O87" s="18" t="n"/>
+      <c r="P87" s="44" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="21" t="n"/>
@@ -5071,6 +5250,7 @@
       <c r="M88" s="20" t="n"/>
       <c r="N88" s="20" t="n"/>
       <c r="O88" s="21" t="n"/>
+      <c r="P88" s="45" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="18" t="n"/>
@@ -5088,6 +5268,7 @@
       <c r="M89" s="17" t="n"/>
       <c r="N89" s="17" t="n"/>
       <c r="O89" s="18" t="n"/>
+      <c r="P89" s="44" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="21" t="n"/>
@@ -5105,6 +5286,7 @@
       <c r="M90" s="20" t="n"/>
       <c r="N90" s="20" t="n"/>
       <c r="O90" s="21" t="n"/>
+      <c r="P90" s="45" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="18" t="n"/>
@@ -5122,6 +5304,7 @@
       <c r="M91" s="17" t="n"/>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="18" t="n"/>
+      <c r="P91" s="44" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="21" t="n"/>
@@ -5139,6 +5322,7 @@
       <c r="M92" s="20" t="n"/>
       <c r="N92" s="20" t="n"/>
       <c r="O92" s="21" t="n"/>
+      <c r="P92" s="45" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="18" t="n"/>
@@ -5156,6 +5340,7 @@
       <c r="M93" s="17" t="n"/>
       <c r="N93" s="17" t="n"/>
       <c r="O93" s="18" t="n"/>
+      <c r="P93" s="44" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="21" t="n"/>
@@ -5173,6 +5358,7 @@
       <c r="M94" s="20" t="n"/>
       <c r="N94" s="20" t="n"/>
       <c r="O94" s="21" t="n"/>
+      <c r="P94" s="45" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="18" t="n"/>
@@ -5190,6 +5376,7 @@
       <c r="M95" s="17" t="n"/>
       <c r="N95" s="17" t="n"/>
       <c r="O95" s="18" t="n"/>
+      <c r="P95" s="44" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="21" t="n"/>
@@ -5207,6 +5394,7 @@
       <c r="M96" s="20" t="n"/>
       <c r="N96" s="20" t="n"/>
       <c r="O96" s="21" t="n"/>
+      <c r="P96" s="45" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="18" t="n"/>
@@ -5224,6 +5412,7 @@
       <c r="M97" s="17" t="n"/>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="18" t="n"/>
+      <c r="P97" s="44" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="21" t="n"/>
@@ -5241,6 +5430,7 @@
       <c r="M98" s="20" t="n"/>
       <c r="N98" s="20" t="n"/>
       <c r="O98" s="21" t="n"/>
+      <c r="P98" s="45" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="18" t="n"/>
@@ -5258,6 +5448,7 @@
       <c r="M99" s="17" t="n"/>
       <c r="N99" s="17" t="n"/>
       <c r="O99" s="18" t="n"/>
+      <c r="P99" s="44" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="21" t="n"/>
@@ -5275,6 +5466,7 @@
       <c r="M100" s="20" t="n"/>
       <c r="N100" s="20" t="n"/>
       <c r="O100" s="21" t="n"/>
+      <c r="P100" s="45" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="18" t="n"/>
@@ -5292,6 +5484,7 @@
       <c r="M101" s="17" t="n"/>
       <c r="N101" s="17" t="n"/>
       <c r="O101" s="18" t="n"/>
+      <c r="P101" s="44" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="21" t="n"/>
@@ -5309,6 +5502,7 @@
       <c r="M102" s="20" t="n"/>
       <c r="N102" s="20" t="n"/>
       <c r="O102" s="21" t="n"/>
+      <c r="P102" s="45" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="18" t="n"/>
@@ -5326,6 +5520,7 @@
       <c r="M103" s="17" t="n"/>
       <c r="N103" s="17" t="n"/>
       <c r="O103" s="18" t="n"/>
+      <c r="P103" s="44" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="21" t="n"/>
@@ -5343,6 +5538,7 @@
       <c r="M104" s="20" t="n"/>
       <c r="N104" s="20" t="n"/>
       <c r="O104" s="21" t="n"/>
+      <c r="P104" s="45" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="18" t="n"/>
@@ -5360,6 +5556,7 @@
       <c r="M105" s="17" t="n"/>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="18" t="n"/>
+      <c r="P105" s="44" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="21" t="n"/>
@@ -5377,6 +5574,7 @@
       <c r="M106" s="20" t="n"/>
       <c r="N106" s="20" t="n"/>
       <c r="O106" s="21" t="n"/>
+      <c r="P106" s="45" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="18" t="n"/>
@@ -5394,6 +5592,7 @@
       <c r="M107" s="17" t="n"/>
       <c r="N107" s="17" t="n"/>
       <c r="O107" s="18" t="n"/>
+      <c r="P107" s="44" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="21" t="n"/>
@@ -5411,6 +5610,7 @@
       <c r="M108" s="20" t="n"/>
       <c r="N108" s="20" t="n"/>
       <c r="O108" s="21" t="n"/>
+      <c r="P108" s="45" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="18" t="n"/>
@@ -5428,6 +5628,7 @@
       <c r="M109" s="17" t="n"/>
       <c r="N109" s="17" t="n"/>
       <c r="O109" s="18" t="n"/>
+      <c r="P109" s="44" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="21" t="n"/>
@@ -5445,6 +5646,7 @@
       <c r="M110" s="20" t="n"/>
       <c r="N110" s="20" t="n"/>
       <c r="O110" s="21" t="n"/>
+      <c r="P110" s="45" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="18" t="n"/>
@@ -5462,6 +5664,7 @@
       <c r="M111" s="17" t="n"/>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="18" t="n"/>
+      <c r="P111" s="44" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="21" t="n"/>
@@ -5479,6 +5682,7 @@
       <c r="M112" s="20" t="n"/>
       <c r="N112" s="20" t="n"/>
       <c r="O112" s="21" t="n"/>
+      <c r="P112" s="45" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="18" t="n"/>
@@ -5496,6 +5700,7 @@
       <c r="M113" s="17" t="n"/>
       <c r="N113" s="17" t="n"/>
       <c r="O113" s="18" t="n"/>
+      <c r="P113" s="44" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="21" t="n"/>
@@ -5513,6 +5718,7 @@
       <c r="M114" s="20" t="n"/>
       <c r="N114" s="20" t="n"/>
       <c r="O114" s="21" t="n"/>
+      <c r="P114" s="45" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="18" t="n"/>
@@ -5530,6 +5736,7 @@
       <c r="M115" s="17" t="n"/>
       <c r="N115" s="17" t="n"/>
       <c r="O115" s="18" t="n"/>
+      <c r="P115" s="44" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="21" t="n"/>
@@ -5547,6 +5754,7 @@
       <c r="M116" s="20" t="n"/>
       <c r="N116" s="20" t="n"/>
       <c r="O116" s="21" t="n"/>
+      <c r="P116" s="45" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="18" t="n"/>
@@ -5564,6 +5772,7 @@
       <c r="M117" s="17" t="n"/>
       <c r="N117" s="17" t="n"/>
       <c r="O117" s="18" t="n"/>
+      <c r="P117" s="44" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="21" t="n"/>
@@ -5581,6 +5790,7 @@
       <c r="M118" s="20" t="n"/>
       <c r="N118" s="20" t="n"/>
       <c r="O118" s="21" t="n"/>
+      <c r="P118" s="45" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="18" t="n"/>
@@ -5598,6 +5808,7 @@
       <c r="M119" s="17" t="n"/>
       <c r="N119" s="17" t="n"/>
       <c r="O119" s="18" t="n"/>
+      <c r="P119" s="44" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="21" t="n"/>
@@ -5615,6 +5826,7 @@
       <c r="M120" s="20" t="n"/>
       <c r="N120" s="20" t="n"/>
       <c r="O120" s="21" t="n"/>
+      <c r="P120" s="45" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="18" t="n"/>
@@ -5632,6 +5844,7 @@
       <c r="M121" s="17" t="n"/>
       <c r="N121" s="17" t="n"/>
       <c r="O121" s="18" t="n"/>
+      <c r="P121" s="44" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="21" t="n"/>
@@ -5649,6 +5862,7 @@
       <c r="M122" s="20" t="n"/>
       <c r="N122" s="20" t="n"/>
       <c r="O122" s="21" t="n"/>
+      <c r="P122" s="45" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="18" t="n"/>
@@ -5666,6 +5880,7 @@
       <c r="M123" s="17" t="n"/>
       <c r="N123" s="17" t="n"/>
       <c r="O123" s="18" t="n"/>
+      <c r="P123" s="44" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="21" t="n"/>
@@ -5683,6 +5898,7 @@
       <c r="M124" s="20" t="n"/>
       <c r="N124" s="20" t="n"/>
       <c r="O124" s="21" t="n"/>
+      <c r="P124" s="45" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="18" t="n"/>
@@ -5700,6 +5916,7 @@
       <c r="M125" s="17" t="n"/>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="18" t="n"/>
+      <c r="P125" s="44" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="21" t="n"/>
@@ -5717,6 +5934,7 @@
       <c r="M126" s="20" t="n"/>
       <c r="N126" s="20" t="n"/>
       <c r="O126" s="21" t="n"/>
+      <c r="P126" s="45" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="18" t="n"/>
@@ -5734,6 +5952,7 @@
       <c r="M127" s="17" t="n"/>
       <c r="N127" s="17" t="n"/>
       <c r="O127" s="18" t="n"/>
+      <c r="P127" s="44" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="21" t="n"/>
@@ -5751,6 +5970,7 @@
       <c r="M128" s="20" t="n"/>
       <c r="N128" s="20" t="n"/>
       <c r="O128" s="21" t="n"/>
+      <c r="P128" s="45" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="18" t="n"/>
@@ -5768,6 +5988,7 @@
       <c r="M129" s="17" t="n"/>
       <c r="N129" s="17" t="n"/>
       <c r="O129" s="18" t="n"/>
+      <c r="P129" s="44" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="21" t="n"/>
@@ -5785,6 +6006,7 @@
       <c r="M130" s="20" t="n"/>
       <c r="N130" s="20" t="n"/>
       <c r="O130" s="21" t="n"/>
+      <c r="P130" s="45" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="18" t="n"/>
@@ -5802,6 +6024,7 @@
       <c r="M131" s="17" t="n"/>
       <c r="N131" s="17" t="n"/>
       <c r="O131" s="18" t="n"/>
+      <c r="P131" s="44" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="21" t="n"/>
@@ -5819,6 +6042,7 @@
       <c r="M132" s="20" t="n"/>
       <c r="N132" s="20" t="n"/>
       <c r="O132" s="21" t="n"/>
+      <c r="P132" s="45" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="18" t="n"/>
@@ -5836,6 +6060,7 @@
       <c r="M133" s="17" t="n"/>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="18" t="n"/>
+      <c r="P133" s="44" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="21" t="n"/>
@@ -5853,6 +6078,7 @@
       <c r="M134" s="20" t="n"/>
       <c r="N134" s="20" t="n"/>
       <c r="O134" s="21" t="n"/>
+      <c r="P134" s="45" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="18" t="n"/>
@@ -5870,6 +6096,7 @@
       <c r="M135" s="17" t="n"/>
       <c r="N135" s="17" t="n"/>
       <c r="O135" s="18" t="n"/>
+      <c r="P135" s="44" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="21" t="n"/>
@@ -5887,6 +6114,7 @@
       <c r="M136" s="20" t="n"/>
       <c r="N136" s="20" t="n"/>
       <c r="O136" s="21" t="n"/>
+      <c r="P136" s="45" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="18" t="n"/>
@@ -5904,6 +6132,7 @@
       <c r="M137" s="17" t="n"/>
       <c r="N137" s="17" t="n"/>
       <c r="O137" s="18" t="n"/>
+      <c r="P137" s="44" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="21" t="n"/>
@@ -5921,6 +6150,7 @@
       <c r="M138" s="20" t="n"/>
       <c r="N138" s="20" t="n"/>
       <c r="O138" s="21" t="n"/>
+      <c r="P138" s="45" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="18" t="n"/>
@@ -5938,6 +6168,7 @@
       <c r="M139" s="17" t="n"/>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="18" t="n"/>
+      <c r="P139" s="44" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="21" t="n"/>
@@ -5955,6 +6186,7 @@
       <c r="M140" s="20" t="n"/>
       <c r="N140" s="20" t="n"/>
       <c r="O140" s="21" t="n"/>
+      <c r="P140" s="45" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="18" t="n"/>
@@ -5972,6 +6204,7 @@
       <c r="M141" s="17" t="n"/>
       <c r="N141" s="17" t="n"/>
       <c r="O141" s="18" t="n"/>
+      <c r="P141" s="44" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="21" t="n"/>
@@ -5989,6 +6222,7 @@
       <c r="M142" s="20" t="n"/>
       <c r="N142" s="20" t="n"/>
       <c r="O142" s="21" t="n"/>
+      <c r="P142" s="45" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="18" t="n"/>
@@ -6006,6 +6240,7 @@
       <c r="M143" s="17" t="n"/>
       <c r="N143" s="17" t="n"/>
       <c r="O143" s="18" t="n"/>
+      <c r="P143" s="44" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="21" t="n"/>
@@ -6023,6 +6258,7 @@
       <c r="M144" s="20" t="n"/>
       <c r="N144" s="20" t="n"/>
       <c r="O144" s="21" t="n"/>
+      <c r="P144" s="45" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="18" t="n"/>
@@ -6040,6 +6276,7 @@
       <c r="M145" s="17" t="n"/>
       <c r="N145" s="17" t="n"/>
       <c r="O145" s="18" t="n"/>
+      <c r="P145" s="44" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="21" t="n"/>
@@ -6057,6 +6294,7 @@
       <c r="M146" s="20" t="n"/>
       <c r="N146" s="20" t="n"/>
       <c r="O146" s="21" t="n"/>
+      <c r="P146" s="45" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="18" t="n"/>
@@ -6074,6 +6312,7 @@
       <c r="M147" s="17" t="n"/>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="18" t="n"/>
+      <c r="P147" s="44" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="21" t="n"/>
@@ -6091,6 +6330,7 @@
       <c r="M148" s="20" t="n"/>
       <c r="N148" s="20" t="n"/>
       <c r="O148" s="21" t="n"/>
+      <c r="P148" s="45" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="18" t="n"/>
@@ -6108,6 +6348,7 @@
       <c r="M149" s="17" t="n"/>
       <c r="N149" s="17" t="n"/>
       <c r="O149" s="18" t="n"/>
+      <c r="P149" s="44" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="21" t="n"/>
@@ -6125,6 +6366,7 @@
       <c r="M150" s="20" t="n"/>
       <c r="N150" s="20" t="n"/>
       <c r="O150" s="21" t="n"/>
+      <c r="P150" s="45" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="18" t="n"/>
@@ -6142,6 +6384,7 @@
       <c r="M151" s="17" t="n"/>
       <c r="N151" s="17" t="n"/>
       <c r="O151" s="18" t="n"/>
+      <c r="P151" s="44" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="21" t="n"/>
@@ -6159,6 +6402,7 @@
       <c r="M152" s="20" t="n"/>
       <c r="N152" s="20" t="n"/>
       <c r="O152" s="21" t="n"/>
+      <c r="P152" s="45" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="18" t="n"/>
@@ -6176,6 +6420,7 @@
       <c r="M153" s="17" t="n"/>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="18" t="n"/>
+      <c r="P153" s="44" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="21" t="n"/>
@@ -6193,6 +6438,7 @@
       <c r="M154" s="20" t="n"/>
       <c r="N154" s="20" t="n"/>
       <c r="O154" s="21" t="n"/>
+      <c r="P154" s="45" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="18" t="n"/>
@@ -6210,6 +6456,7 @@
       <c r="M155" s="17" t="n"/>
       <c r="N155" s="17" t="n"/>
       <c r="O155" s="18" t="n"/>
+      <c r="P155" s="44" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="21" t="n"/>
@@ -6227,6 +6474,7 @@
       <c r="M156" s="20" t="n"/>
       <c r="N156" s="20" t="n"/>
       <c r="O156" s="21" t="n"/>
+      <c r="P156" s="45" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="18" t="n"/>
@@ -6244,6 +6492,7 @@
       <c r="M157" s="17" t="n"/>
       <c r="N157" s="17" t="n"/>
       <c r="O157" s="18" t="n"/>
+      <c r="P157" s="44" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="21" t="n"/>
@@ -6261,6 +6510,7 @@
       <c r="M158" s="20" t="n"/>
       <c r="N158" s="20" t="n"/>
       <c r="O158" s="21" t="n"/>
+      <c r="P158" s="45" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="18" t="n"/>
@@ -6278,6 +6528,7 @@
       <c r="M159" s="17" t="n"/>
       <c r="N159" s="17" t="n"/>
       <c r="O159" s="18" t="n"/>
+      <c r="P159" s="44" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="21" t="n"/>
@@ -6295,6 +6546,7 @@
       <c r="M160" s="20" t="n"/>
       <c r="N160" s="20" t="n"/>
       <c r="O160" s="21" t="n"/>
+      <c r="P160" s="45" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="18" t="n"/>
@@ -6312,6 +6564,7 @@
       <c r="M161" s="17" t="n"/>
       <c r="N161" s="17" t="n"/>
       <c r="O161" s="18" t="n"/>
+      <c r="P161" s="44" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="21" t="n"/>
@@ -6329,6 +6582,7 @@
       <c r="M162" s="20" t="n"/>
       <c r="N162" s="20" t="n"/>
       <c r="O162" s="21" t="n"/>
+      <c r="P162" s="45" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="18" t="n"/>
@@ -6346,6 +6600,7 @@
       <c r="M163" s="17" t="n"/>
       <c r="N163" s="17" t="n"/>
       <c r="O163" s="18" t="n"/>
+      <c r="P163" s="44" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="21" t="n"/>
@@ -6363,6 +6618,7 @@
       <c r="M164" s="20" t="n"/>
       <c r="N164" s="20" t="n"/>
       <c r="O164" s="21" t="n"/>
+      <c r="P164" s="45" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="18" t="n"/>
@@ -6380,6 +6636,7 @@
       <c r="M165" s="17" t="n"/>
       <c r="N165" s="17" t="n"/>
       <c r="O165" s="18" t="n"/>
+      <c r="P165" s="44" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="21" t="n"/>
@@ -6397,6 +6654,7 @@
       <c r="M166" s="20" t="n"/>
       <c r="N166" s="20" t="n"/>
       <c r="O166" s="21" t="n"/>
+      <c r="P166" s="45" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="18" t="n"/>
@@ -6414,6 +6672,7 @@
       <c r="M167" s="17" t="n"/>
       <c r="N167" s="17" t="n"/>
       <c r="O167" s="18" t="n"/>
+      <c r="P167" s="44" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="21" t="n"/>
@@ -6431,6 +6690,7 @@
       <c r="M168" s="20" t="n"/>
       <c r="N168" s="20" t="n"/>
       <c r="O168" s="21" t="n"/>
+      <c r="P168" s="45" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="18" t="n"/>
@@ -6448,6 +6708,7 @@
       <c r="M169" s="17" t="n"/>
       <c r="N169" s="17" t="n"/>
       <c r="O169" s="18" t="n"/>
+      <c r="P169" s="44" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="21" t="n"/>
@@ -6465,6 +6726,7 @@
       <c r="M170" s="20" t="n"/>
       <c r="N170" s="20" t="n"/>
       <c r="O170" s="21" t="n"/>
+      <c r="P170" s="45" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="18" t="n"/>
@@ -6482,6 +6744,7 @@
       <c r="M171" s="17" t="n"/>
       <c r="N171" s="17" t="n"/>
       <c r="O171" s="18" t="n"/>
+      <c r="P171" s="44" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="21" t="n"/>
@@ -6499,6 +6762,7 @@
       <c r="M172" s="20" t="n"/>
       <c r="N172" s="20" t="n"/>
       <c r="O172" s="21" t="n"/>
+      <c r="P172" s="45" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="18" t="n"/>
@@ -6516,6 +6780,7 @@
       <c r="M173" s="17" t="n"/>
       <c r="N173" s="17" t="n"/>
       <c r="O173" s="18" t="n"/>
+      <c r="P173" s="44" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="21" t="n"/>
@@ -6533,6 +6798,7 @@
       <c r="M174" s="20" t="n"/>
       <c r="N174" s="20" t="n"/>
       <c r="O174" s="21" t="n"/>
+      <c r="P174" s="45" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="18" t="n"/>
@@ -6550,6 +6816,7 @@
       <c r="M175" s="17" t="n"/>
       <c r="N175" s="17" t="n"/>
       <c r="O175" s="18" t="n"/>
+      <c r="P175" s="44" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="21" t="n"/>
@@ -6567,6 +6834,7 @@
       <c r="M176" s="20" t="n"/>
       <c r="N176" s="20" t="n"/>
       <c r="O176" s="21" t="n"/>
+      <c r="P176" s="45" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="18" t="n"/>
@@ -6584,6 +6852,7 @@
       <c r="M177" s="17" t="n"/>
       <c r="N177" s="17" t="n"/>
       <c r="O177" s="18" t="n"/>
+      <c r="P177" s="44" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="21" t="n"/>
@@ -6601,6 +6870,7 @@
       <c r="M178" s="20" t="n"/>
       <c r="N178" s="20" t="n"/>
       <c r="O178" s="21" t="n"/>
+      <c r="P178" s="45" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="18" t="n"/>
@@ -6618,6 +6888,7 @@
       <c r="M179" s="17" t="n"/>
       <c r="N179" s="17" t="n"/>
       <c r="O179" s="18" t="n"/>
+      <c r="P179" s="44" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="21" t="n"/>
@@ -6635,6 +6906,7 @@
       <c r="M180" s="20" t="n"/>
       <c r="N180" s="20" t="n"/>
       <c r="O180" s="21" t="n"/>
+      <c r="P180" s="45" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="18" t="n"/>
@@ -6652,6 +6924,7 @@
       <c r="M181" s="17" t="n"/>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="18" t="n"/>
+      <c r="P181" s="44" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="21" t="n"/>
@@ -6669,6 +6942,7 @@
       <c r="M182" s="20" t="n"/>
       <c r="N182" s="20" t="n"/>
       <c r="O182" s="21" t="n"/>
+      <c r="P182" s="45" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="18" t="n"/>
@@ -6686,6 +6960,7 @@
       <c r="M183" s="17" t="n"/>
       <c r="N183" s="17" t="n"/>
       <c r="O183" s="18" t="n"/>
+      <c r="P183" s="44" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="21" t="n"/>
@@ -6703,6 +6978,7 @@
       <c r="M184" s="20" t="n"/>
       <c r="N184" s="20" t="n"/>
       <c r="O184" s="21" t="n"/>
+      <c r="P184" s="45" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="18" t="n"/>
@@ -6720,6 +6996,7 @@
       <c r="M185" s="17" t="n"/>
       <c r="N185" s="17" t="n"/>
       <c r="O185" s="18" t="n"/>
+      <c r="P185" s="44" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="21" t="n"/>
@@ -6737,6 +7014,7 @@
       <c r="M186" s="20" t="n"/>
       <c r="N186" s="20" t="n"/>
       <c r="O186" s="21" t="n"/>
+      <c r="P186" s="45" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="18" t="n"/>
@@ -6754,6 +7032,7 @@
       <c r="M187" s="17" t="n"/>
       <c r="N187" s="17" t="n"/>
       <c r="O187" s="18" t="n"/>
+      <c r="P187" s="44" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="21" t="n"/>
@@ -6771,6 +7050,7 @@
       <c r="M188" s="20" t="n"/>
       <c r="N188" s="20" t="n"/>
       <c r="O188" s="21" t="n"/>
+      <c r="P188" s="45" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="18" t="n"/>
@@ -6788,6 +7068,7 @@
       <c r="M189" s="17" t="n"/>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="18" t="n"/>
+      <c r="P189" s="44" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="21" t="n"/>
@@ -6805,6 +7086,7 @@
       <c r="M190" s="20" t="n"/>
       <c r="N190" s="20" t="n"/>
       <c r="O190" s="21" t="n"/>
+      <c r="P190" s="45" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="18" t="n"/>
@@ -6822,6 +7104,7 @@
       <c r="M191" s="17" t="n"/>
       <c r="N191" s="17" t="n"/>
       <c r="O191" s="18" t="n"/>
+      <c r="P191" s="44" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="21" t="n"/>
@@ -6839,6 +7122,7 @@
       <c r="M192" s="20" t="n"/>
       <c r="N192" s="20" t="n"/>
       <c r="O192" s="21" t="n"/>
+      <c r="P192" s="45" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="18" t="n"/>
@@ -6856,6 +7140,7 @@
       <c r="M193" s="17" t="n"/>
       <c r="N193" s="17" t="n"/>
       <c r="O193" s="18" t="n"/>
+      <c r="P193" s="44" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="21" t="n"/>
@@ -6873,6 +7158,7 @@
       <c r="M194" s="20" t="n"/>
       <c r="N194" s="20" t="n"/>
       <c r="O194" s="21" t="n"/>
+      <c r="P194" s="45" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="18" t="n"/>
@@ -6890,6 +7176,7 @@
       <c r="M195" s="17" t="n"/>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="18" t="n"/>
+      <c r="P195" s="44" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="21" t="n"/>
@@ -6907,6 +7194,7 @@
       <c r="M196" s="20" t="n"/>
       <c r="N196" s="20" t="n"/>
       <c r="O196" s="21" t="n"/>
+      <c r="P196" s="45" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="18" t="n"/>
@@ -6924,6 +7212,7 @@
       <c r="M197" s="17" t="n"/>
       <c r="N197" s="17" t="n"/>
       <c r="O197" s="18" t="n"/>
+      <c r="P197" s="44" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="21" t="n"/>
@@ -6941,6 +7230,7 @@
       <c r="M198" s="20" t="n"/>
       <c r="N198" s="20" t="n"/>
       <c r="O198" s="21" t="n"/>
+      <c r="P198" s="45" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="18" t="n"/>
@@ -6958,6 +7248,7 @@
       <c r="M199" s="17" t="n"/>
       <c r="N199" s="17" t="n"/>
       <c r="O199" s="18" t="n"/>
+      <c r="P199" s="44" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="21" t="n"/>
@@ -6975,6 +7266,7 @@
       <c r="M200" s="20" t="n"/>
       <c r="N200" s="20" t="n"/>
       <c r="O200" s="21" t="n"/>
+      <c r="P200" s="45" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="18" t="n"/>
@@ -6992,6 +7284,7 @@
       <c r="M201" s="17" t="n"/>
       <c r="N201" s="17" t="n"/>
       <c r="O201" s="18" t="n"/>
+      <c r="P201" s="44" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="21" t="n"/>
@@ -7009,6 +7302,7 @@
       <c r="M202" s="20" t="n"/>
       <c r="N202" s="20" t="n"/>
       <c r="O202" s="21" t="n"/>
+      <c r="P202" s="45" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="18" t="n"/>
@@ -7026,6 +7320,7 @@
       <c r="M203" s="17" t="n"/>
       <c r="N203" s="17" t="n"/>
       <c r="O203" s="18" t="n"/>
+      <c r="P203" s="44" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="21" t="n"/>
@@ -7043,11 +7338,12 @@
       <c r="M204" s="20" t="n"/>
       <c r="N204" s="20" t="n"/>
       <c r="O204" s="21" t="n"/>
+      <c r="P204" s="45" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G204">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -7060,7 +7356,7 @@
       <formula>"Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="F5:F204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=YesNoList</formula1>
     </dataValidation>
@@ -7084,6 +7380,9 @@
     </dataValidation>
     <dataValidation sqref="N5:N204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=YesNoList</formula1>
+    </dataValidation>
+    <dataValidation sqref="P5:P204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=TableList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7180,7 +7479,7 @@
           <t>Beef</t>
         </is>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="46">
         <f>SUMPRODUCT((GuestMeal="Beef")*(GuestRsvp="Accepted")*IFERROR(GuestSeats,0))</f>
         <v/>
       </c>
@@ -7220,7 +7519,7 @@
           <t>Fish</t>
         </is>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="46">
         <f>SUMPRODUCT((GuestMeal="Fish")*(GuestRsvp="Accepted")*IFERROR(GuestSeats,0))</f>
         <v/>
       </c>
@@ -7231,7 +7530,7 @@
           <t>RSVP Completion %</t>
         </is>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="47">
         <f>IFERROR(COUNTIF(GuestRsvp,"Accepted")+COUNTIF(GuestRsvp,"Declined"),0)/MAX(COUNTA(GuestName),1)</f>
         <v/>
       </c>
@@ -7251,7 +7550,7 @@
           <t>Attendance %</t>
         </is>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="47">
         <f>IFERROR(SUMPRODUCT((GuestRsvp="Accepted")*IFERROR(GuestSeats,0))/MAX(SUMPRODUCT((GuestInvited="Yes")*IFERROR(GuestSeats,0)),1),0)</f>
         <v/>
       </c>
@@ -7260,7 +7559,7 @@
           <t>Vegan</t>
         </is>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="46">
         <f>SUMPRODUCT((GuestMeal="Vegan")*(GuestRsvp="Accepted")*IFERROR(GuestSeats,0))</f>
         <v/>
       </c>
@@ -7282,7 +7581,7 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="46">
         <f>SUMPRODUCT((GuestMeal="None")*(GuestRsvp="Accepted")*IFERROR(GuestSeats,0))</f>
         <v/>
       </c>
@@ -7305,7 +7604,7 @@
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="46">
         <f>COUNTIF(GuestRsvp,"Accepted")</f>
         <v/>
       </c>
@@ -7316,7 +7615,7 @@
           <t>Declined</t>
         </is>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="46">
         <f>COUNTIF(GuestRsvp,"Declined")</f>
         <v/>
       </c>
@@ -7327,7 +7626,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="46">
         <f>COUNTIF(GuestRsvp,"Pending")</f>
         <v/>
       </c>
@@ -7351,15 +7650,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -7372,7 +7675,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Assign tables with live capacity warnings and VIP flags.</t>
+          <t xml:space="preserve">  Assign guests to tables on the Guest tab — rosters here fill in automatically. Pick a table in the Inspector to see who's seated.</t>
         </is>
       </c>
     </row>
@@ -7383,6 +7686,10 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -7392,7 +7699,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Assigned Guests</t>
+          <t>Assigned Guests (auto)</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -7415,20 +7722,25 @@
           <t>VIP / Notes</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>🔎  TABLE INSPECTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Bride, Groom, MOH, Best Man, parents (8)</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="n">
-        <v>8</v>
+      <c r="B5" s="18">
+        <f t="array" ref="B5">TEXTJOIN(", ",TRUE,IF(GuestTable=$A5,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C5" s="40">
+        <f>SUMPRODUCT((GuestTable=$A5)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D5" s="40" t="n">
         <v>10</v>
@@ -7439,23 +7751,34 @@
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>Head table — VIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>Head table — ★ VIP</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Select a Table</t>
+        </is>
+      </c>
+      <c r="I5" s="48" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="J5" s="49" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Bennett family</t>
-        </is>
-      </c>
-      <c r="C6" s="41" t="n">
-        <v>9</v>
+      <c r="B6" s="21">
+        <f t="array" ref="B6">TEXTJOIN(", ",TRUE,IF(GuestTable=$A6,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C6" s="41">
+        <f>SUMPRODUCT((GuestTable=$A6)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D6" s="41" t="n">
         <v>10</v>
@@ -7469,20 +7792,29 @@
           <t>VIP — grandparents</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Seated</t>
+        </is>
+      </c>
+      <c r="I6" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Table 3</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Carter family</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="n">
-        <v>10</v>
+      <c r="B7" s="18">
+        <f t="array" ref="B7">TEXTJOIN(", ",TRUE,IF(GuestTable=$A7,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C7" s="40">
+        <f>SUMPRODUCT((GuestTable=$A7)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D7" s="40" t="n">
         <v>10</v>
@@ -7492,20 +7824,29 @@
         <v/>
       </c>
       <c r="F7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="I7" s="50">
+        <f>IFERROR(INDEX($D$5:$D$24,MATCH(InspectTable,$A$5:$A$24,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Table 4</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>College friends</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="n">
-        <v>8</v>
+      <c r="B8" s="21">
+        <f t="array" ref="B8">TEXTJOIN(", ",TRUE,IF(GuestTable=$A8,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C8" s="41">
+        <f>SUMPRODUCT((GuestTable=$A8)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D8" s="41" t="n">
         <v>10</v>
@@ -7515,20 +7856,29 @@
         <v/>
       </c>
       <c r="F8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Open Seats</t>
+        </is>
+      </c>
+      <c r="I8" s="50">
+        <f>IF(I7="","",I7-I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Table 5</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Work friends</t>
-        </is>
-      </c>
-      <c r="C9" s="40" t="n">
-        <v>7</v>
+      <c r="B9" s="18">
+        <f t="array" ref="B9">TEXTJOIN(", ",TRUE,IF(GuestTable=$A9,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C9" s="40">
+        <f>SUMPRODUCT((GuestTable=$A9)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D9" s="40" t="n">
         <v>10</v>
@@ -7539,19 +7889,19 @@
       </c>
       <c r="F9" s="18" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Table 6</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Patel + Rivera families</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="n">
-        <v>10</v>
+      <c r="B10" s="21">
+        <f t="array" ref="B10">TEXTJOIN(", ",TRUE,IF(GuestTable=$A10,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="41">
+        <f>SUMPRODUCT((GuestTable=$A10)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D10" s="41" t="n">
         <v>10</v>
@@ -7565,20 +7915,25 @@
           <t>1 highchair needed</t>
         </is>
       </c>
-    </row>
-    <row r="11">
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>WHO'S SITTING HERE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Table 7</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Neighbors &amp; family friends</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="n">
-        <v>9</v>
+      <c r="B11" s="18">
+        <f t="array" ref="B11">TEXTJOIN(", ",TRUE,IF(GuestTable=$A11,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C11" s="40">
+        <f>SUMPRODUCT((GuestTable=$A11)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D11" s="40" t="n">
         <v>10</v>
@@ -7588,20 +7943,24 @@
         <v/>
       </c>
       <c r="F11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="H11" s="51">
+        <f t="array" ref="H11">TEXTJOIN(", ",TRUE,IF(GuestTable=InspectTable,GuestName&amp;" ("&amp;IFERROR(GuestSeats,0)&amp;")",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Table 8</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Plus-ones &amp; misc</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="n">
-        <v>6</v>
+      <c r="B12" s="21">
+        <f t="array" ref="B12">TEXTJOIN(", ",TRUE,IF(GuestTable=$A12,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C12" s="41">
+        <f>SUMPRODUCT((GuestTable=$A12)*IFERROR(GuestSeats,0))</f>
+        <v/>
       </c>
       <c r="D12" s="41" t="n">
         <v>10</v>
@@ -7612,306 +7971,420 @@
       </c>
       <c r="F12" s="21" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Table 9</t>
+        </is>
+      </c>
+      <c r="B13" s="18">
+        <f t="array" ref="B13">TEXTJOIN(", ",TRUE,IF(GuestTable=$A13,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C13" s="40">
+        <f>SUMPRODUCT((GuestTable=$A13)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>10</v>
+      </c>
       <c r="E13" s="40">
         <f>IF(D13="","",D13-IFERROR(C13,0))</f>
         <v/>
       </c>
-      <c r="F13" s="18" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n"/>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
+      <c r="F13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Table 10</t>
+        </is>
+      </c>
+      <c r="B14" s="21">
+        <f t="array" ref="B14">TEXTJOIN(", ",TRUE,IF(GuestTable=$A14,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C14" s="41">
+        <f>SUMPRODUCT((GuestTable=$A14)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E14" s="41">
         <f>IF(D14="","",D14-IFERROR(C14,0))</f>
         <v/>
       </c>
-      <c r="F14" s="21" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
+      <c r="F14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Table 11</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f t="array" ref="B15">TEXTJOIN(", ",TRUE,IF(GuestTable=$A15,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C15" s="40">
+        <f>SUMPRODUCT((GuestTable=$A15)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>10</v>
+      </c>
       <c r="E15" s="40">
         <f>IF(D15="","",D15-IFERROR(C15,0))</f>
         <v/>
       </c>
-      <c r="F15" s="18" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n"/>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
+      <c r="F15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Table 12</t>
+        </is>
+      </c>
+      <c r="B16" s="21">
+        <f t="array" ref="B16">TEXTJOIN(", ",TRUE,IF(GuestTable=$A16,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C16" s="41">
+        <f>SUMPRODUCT((GuestTable=$A16)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E16" s="41">
         <f>IF(D16="","",D16-IFERROR(C16,0))</f>
         <v/>
       </c>
-      <c r="F16" s="21" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="40" t="n"/>
-      <c r="D17" s="40" t="n"/>
+      <c r="F16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Table 13</t>
+        </is>
+      </c>
+      <c r="B17" s="18">
+        <f t="array" ref="B17">TEXTJOIN(", ",TRUE,IF(GuestTable=$A17,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C17" s="40">
+        <f>SUMPRODUCT((GuestTable=$A17)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>10</v>
+      </c>
       <c r="E17" s="40">
         <f>IF(D17="","",D17-IFERROR(C17,0))</f>
         <v/>
       </c>
-      <c r="F17" s="18" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
+      <c r="F17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Table 14</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f t="array" ref="B18">TEXTJOIN(", ",TRUE,IF(GuestTable=$A18,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C18" s="41">
+        <f>SUMPRODUCT((GuestTable=$A18)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D18" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E18" s="41">
         <f>IF(D18="","",D18-IFERROR(C18,0))</f>
         <v/>
       </c>
-      <c r="F18" s="21" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="40" t="n"/>
-      <c r="D19" s="40" t="n"/>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>MEAL COUNTS AT THIS TABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Table 15</t>
+        </is>
+      </c>
+      <c r="B19" s="18">
+        <f t="array" ref="B19">TEXTJOIN(", ",TRUE,IF(GuestTable=$A19,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C19" s="40">
+        <f>SUMPRODUCT((GuestTable=$A19)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D19" s="40" t="n">
+        <v>10</v>
+      </c>
       <c r="E19" s="40">
         <f>IF(D19="","",D19-IFERROR(C19,0))</f>
         <v/>
       </c>
-      <c r="F19" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n"/>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
+      <c r="F19" s="18" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="I19" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*(GuestMeal="Beef")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Table 16</t>
+        </is>
+      </c>
+      <c r="B20" s="21">
+        <f t="array" ref="B20">TEXTJOIN(", ",TRUE,IF(GuestTable=$A20,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C20" s="41">
+        <f>SUMPRODUCT((GuestTable=$A20)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D20" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E20" s="41">
         <f>IF(D20="","",D20-IFERROR(C20,0))</f>
         <v/>
       </c>
-      <c r="F20" s="21" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="40" t="n"/>
-      <c r="D21" s="40" t="n"/>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="I20" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*(GuestMeal="Chicken")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Table 17</t>
+        </is>
+      </c>
+      <c r="B21" s="18">
+        <f t="array" ref="B21">TEXTJOIN(", ",TRUE,IF(GuestTable=$A21,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C21" s="40">
+        <f>SUMPRODUCT((GuestTable=$A21)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D21" s="40" t="n">
+        <v>10</v>
+      </c>
       <c r="E21" s="40">
         <f>IF(D21="","",D21-IFERROR(C21,0))</f>
         <v/>
       </c>
-      <c r="F21" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="n"/>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
+      <c r="F21" s="18" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="I21" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*(GuestMeal="Fish")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Table 18</t>
+        </is>
+      </c>
+      <c r="B22" s="21">
+        <f t="array" ref="B22">TEXTJOIN(", ",TRUE,IF(GuestTable=$A22,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C22" s="41">
+        <f>SUMPRODUCT((GuestTable=$A22)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E22" s="41">
         <f>IF(D22="","",D22-IFERROR(C22,0))</f>
         <v/>
       </c>
-      <c r="F22" s="21" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="40" t="n"/>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="I22" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*(GuestMeal="Vegetarian")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Table 19</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
+        <f t="array" ref="B23">TEXTJOIN(", ",TRUE,IF(GuestTable=$A23,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C23" s="40">
+        <f>SUMPRODUCT((GuestTable=$A23)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D23" s="40" t="n">
+        <v>10</v>
+      </c>
       <c r="E23" s="40">
         <f>IF(D23="","",D23-IFERROR(C23,0))</f>
         <v/>
       </c>
-      <c r="F23" s="18" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="n"/>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="41" t="n"/>
-      <c r="D24" s="41" t="n"/>
+      <c r="F23" s="18" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+      <c r="I23" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*(GuestMeal="Vegan")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Table 20</t>
+        </is>
+      </c>
+      <c r="B24" s="21">
+        <f t="array" ref="B24">TEXTJOIN(", ",TRUE,IF(GuestTable=$A24,GuestName,""))</f>
+        <v/>
+      </c>
+      <c r="C24" s="41">
+        <f>SUMPRODUCT((GuestTable=$A24)*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
+      <c r="D24" s="41" t="n">
+        <v>10</v>
+      </c>
       <c r="E24" s="41">
         <f>IF(D24="","",D24-IFERROR(C24,0))</f>
         <v/>
       </c>
-      <c r="F24" s="21" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="40" t="n"/>
-      <c r="D25" s="40" t="n"/>
-      <c r="E25" s="40">
-        <f>IF(D25="","",D25-IFERROR(C25,0))</f>
-        <v/>
-      </c>
-      <c r="F25" s="18" t="n"/>
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="I24" s="50">
+        <f>SUMPRODUCT((GuestTable=InspectTable)*(GuestMeal="Kids")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n"/>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="41" t="n"/>
-      <c r="E26" s="41">
-        <f>IF(D26="","",D26-IFERROR(C26,0))</f>
-        <v/>
-      </c>
-      <c r="F26" s="21" t="n"/>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>CAPACITY SUMMARY</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="18" t="n"/>
-      <c r="C27" s="40" t="n"/>
-      <c r="D27" s="40" t="n"/>
-      <c r="E27" s="40">
-        <f>IF(D27="","",D27-IFERROR(C27,0))</f>
-        <v/>
-      </c>
-      <c r="F27" s="18" t="n"/>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Total Seated</t>
+        </is>
+      </c>
+      <c r="F27" s="50">
+        <f>SUM(C5:C24)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n"/>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="41">
-        <f>IF(D28="","",D28-IFERROR(C28,0))</f>
-        <v/>
-      </c>
-      <c r="F28" s="21" t="n"/>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Total Capacity</t>
+        </is>
+      </c>
+      <c r="F28" s="50">
+        <f>SUM(D5:D24)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="40" t="n"/>
-      <c r="D29" s="40" t="n"/>
-      <c r="E29" s="40">
-        <f>IF(D29="","",D29-IFERROR(C29,0))</f>
-        <v/>
-      </c>
-      <c r="F29" s="18" t="n"/>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Seats Open</t>
+        </is>
+      </c>
+      <c r="F29" s="50">
+        <f>SUM(E5:E24)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="n"/>
-      <c r="B30" s="21" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41">
-        <f>IF(D30="","",D30-IFERROR(C30,0))</f>
-        <v/>
-      </c>
-      <c r="F30" s="21" t="n"/>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Accepted Guests (need seats)</t>
+        </is>
+      </c>
+      <c r="F30" s="50">
+        <f>SUMPRODUCT((GuestRsvp="Accepted")*IFERROR(GuestSeats,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="40" t="n"/>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="40">
-        <f>IF(D31="","",D31-IFERROR(C31,0))</f>
-        <v/>
-      </c>
-      <c r="F31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="n"/>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="41" t="n"/>
-      <c r="D32" s="41" t="n"/>
-      <c r="E32" s="41">
-        <f>IF(D32="","",D32-IFERROR(C32,0))</f>
-        <v/>
-      </c>
-      <c r="F32" s="21" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="n"/>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="40" t="n"/>
-      <c r="D33" s="40" t="n"/>
-      <c r="E33" s="40">
-        <f>IF(D33="","",D33-IFERROR(C33,0))</f>
-        <v/>
-      </c>
-      <c r="F33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="n"/>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="41" t="n"/>
-      <c r="D34" s="41" t="n"/>
-      <c r="E34" s="41">
-        <f>IF(D34="","",D34-IFERROR(C34,0))</f>
-        <v/>
-      </c>
-      <c r="F34" s="21" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>CAPACITY SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>Total Seated</t>
-        </is>
-      </c>
-      <c r="B39" s="46">
-        <f>SUM(C5:C34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>Total Capacity</t>
-        </is>
-      </c>
-      <c r="B40" s="46">
-        <f>SUM(D5:D34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Seats Open</t>
-        </is>
-      </c>
-      <c r="B41" s="46">
-        <f>SUM(E5:E34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>Accepted Guests (need seats)</t>
-        </is>
-      </c>
-      <c r="B42" s="46">
-        <f>SUMPRODUCT((GuestRsvp="Accepted")*IFERROR(GuestSeats,0))</f>
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Guests Not Yet Seated</t>
+        </is>
+      </c>
+      <c r="F31" s="50">
+        <f>SUMPRODUCT((GuestRsvp="Accepted")*(GuestTable="")*IFERROR(GuestSeats,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H11:J16"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F34">
+  <conditionalFormatting sqref="A5:F24">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>AND($C5&lt;&gt;"",$C5&gt;$D5)</formula>
     </cfRule>
@@ -7919,11 +8392,16 @@
       <formula>ISNUMBER(SEARCH("VIP",$F5))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E34">
+  <conditionalFormatting sqref="E5:E24">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="I5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=TableList</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15466,25 +15944,25 @@
       <c r="F3" s="3" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>⬆ Venue
 Drop image here</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>⬆ Dress
 Drop image here</t>
         </is>
       </c>
-      <c r="D5" s="47" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>⬆ Florals
 Drop image here</t>
         </is>
       </c>
-      <c r="E5" s="47" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>⬆ Cake
 Drop image here</t>
@@ -15492,28 +15970,28 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="48" t="n"/>
-      <c r="C6" s="48" t="n"/>
-      <c r="D6" s="48" t="n"/>
-      <c r="E6" s="48" t="n"/>
+      <c r="B6" s="53" t="n"/>
+      <c r="C6" s="53" t="n"/>
+      <c r="D6" s="53" t="n"/>
+      <c r="E6" s="53" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="48" t="n"/>
-      <c r="C7" s="48" t="n"/>
-      <c r="D7" s="48" t="n"/>
-      <c r="E7" s="48" t="n"/>
+      <c r="B7" s="53" t="n"/>
+      <c r="C7" s="53" t="n"/>
+      <c r="D7" s="53" t="n"/>
+      <c r="E7" s="53" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="48" t="n"/>
-      <c r="C8" s="48" t="n"/>
-      <c r="D8" s="48" t="n"/>
-      <c r="E8" s="48" t="n"/>
+      <c r="B8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="48" t="n"/>
-      <c r="C9" s="48" t="n"/>
-      <c r="D9" s="48" t="n"/>
-      <c r="E9" s="48" t="n"/>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="13" t="inlineStr">
@@ -15550,25 +16028,25 @@
       <c r="E12" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>⬆ Hair
 Drop image here</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="52" t="inlineStr">
         <is>
           <t>⬆ Makeup
 Drop image here</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="52" t="inlineStr">
         <is>
           <t>⬆ Decor
 Drop image here</t>
         </is>
       </c>
-      <c r="E14" s="47" t="inlineStr">
+      <c r="E14" s="52" t="inlineStr">
         <is>
           <t>⬆ Tablescapes
 Drop image here</t>
@@ -15576,28 +16054,28 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="48" t="n"/>
-      <c r="C15" s="48" t="n"/>
-      <c r="D15" s="48" t="n"/>
-      <c r="E15" s="48" t="n"/>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="48" t="n"/>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="48" t="n"/>
-      <c r="E16" s="48" t="n"/>
+      <c r="B16" s="53" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
+      <c r="E16" s="53" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="48" t="n"/>
-      <c r="E17" s="48" t="n"/>
+      <c r="B17" s="53" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
+      <c r="E17" s="53" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="48" t="n"/>
-      <c r="C18" s="48" t="n"/>
-      <c r="D18" s="48" t="n"/>
-      <c r="E18" s="48" t="n"/>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
+      <c r="E18" s="53" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="13" t="inlineStr">
@@ -15634,25 +16112,25 @@
       <c r="E21" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="47" t="inlineStr">
+      <c r="B23" s="52" t="inlineStr">
         <is>
           <t>⬆ Stationery
 Drop image here</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" s="52" t="inlineStr">
         <is>
           <t>⬆ Color Palette
 Drop image here</t>
         </is>
       </c>
-      <c r="D23" s="47" t="inlineStr">
+      <c r="D23" s="52" t="inlineStr">
         <is>
           <t>⬆ Bouquets
 Drop image here</t>
         </is>
       </c>
-      <c r="E23" s="47" t="inlineStr">
+      <c r="E23" s="52" t="inlineStr">
         <is>
           <t>⬆ Photo Poses
 Drop image here</t>
@@ -15660,28 +16138,28 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="48" t="n"/>
-      <c r="C24" s="48" t="n"/>
-      <c r="D24" s="48" t="n"/>
-      <c r="E24" s="48" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+      <c r="E24" s="53" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="48" t="n"/>
-      <c r="C25" s="48" t="n"/>
-      <c r="D25" s="48" t="n"/>
-      <c r="E25" s="48" t="n"/>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+      <c r="E25" s="53" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="48" t="n"/>
-      <c r="C26" s="48" t="n"/>
-      <c r="D26" s="48" t="n"/>
-      <c r="E26" s="48" t="n"/>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
+      <c r="E26" s="53" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="48" t="n"/>
-      <c r="C27" s="48" t="n"/>
-      <c r="D27" s="48" t="n"/>
-      <c r="E27" s="48" t="n"/>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
+      <c r="E27" s="53" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="13" t="inlineStr">
@@ -15718,25 +16196,25 @@
       <c r="E30" s="14" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="47" t="inlineStr">
+      <c r="B32" s="52" t="inlineStr">
         <is>
           <t>⬆ Reception Setup
 Drop image here</t>
         </is>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C32" s="52" t="inlineStr">
         <is>
           <t>⬆ Lighting
 Drop image here</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D32" s="52" t="inlineStr">
         <is>
           <t>⬆ Favors
 Drop image here</t>
         </is>
       </c>
-      <c r="E32" s="47" t="inlineStr">
+      <c r="E32" s="52" t="inlineStr">
         <is>
           <t>⬆ Travel Ideas
 Drop image here</t>
@@ -15744,28 +16222,28 @@
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="48" t="n"/>
-      <c r="C33" s="48" t="n"/>
-      <c r="D33" s="48" t="n"/>
-      <c r="E33" s="48" t="n"/>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+      <c r="E33" s="53" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="48" t="n"/>
-      <c r="C34" s="48" t="n"/>
-      <c r="D34" s="48" t="n"/>
-      <c r="E34" s="48" t="n"/>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
+      <c r="E34" s="53" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="48" t="n"/>
-      <c r="C35" s="48" t="n"/>
-      <c r="D35" s="48" t="n"/>
-      <c r="E35" s="48" t="n"/>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="53" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="48" t="n"/>
-      <c r="C36" s="48" t="n"/>
-      <c r="D36" s="48" t="n"/>
-      <c r="E36" s="48" t="n"/>
+      <c r="B36" s="53" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
+      <c r="E36" s="53" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="13" t="inlineStr">
@@ -15906,7 +16384,7 @@
           <t>Dress + garment bag</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15916,7 +16394,7 @@
           <t>Passports</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15926,7 +16404,7 @@
           <t>Sewing kit</t>
         </is>
       </c>
-      <c r="F5" s="49" t="inlineStr">
+      <c r="F5" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15936,7 +16414,7 @@
           <t>Guest book + pen</t>
         </is>
       </c>
-      <c r="H5" s="49" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15948,7 +16426,7 @@
           <t>Veil</t>
         </is>
       </c>
-      <c r="B6" s="50" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15958,7 +16436,7 @@
           <t>Tickets / confirmations</t>
         </is>
       </c>
-      <c r="D6" s="50" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15968,7 +16446,7 @@
           <t>Safety pins</t>
         </is>
       </c>
-      <c r="F6" s="50" t="inlineStr">
+      <c r="F6" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15978,7 +16456,7 @@
           <t>Card box</t>
         </is>
       </c>
-      <c r="H6" s="50" t="inlineStr">
+      <c r="H6" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -15990,7 +16468,7 @@
           <t>Shoes</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16000,7 +16478,7 @@
           <t>Swimwear</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16010,7 +16488,7 @@
           <t>Stain remover</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
+      <c r="F7" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16020,7 +16498,7 @@
           <t>Toasting flutes</t>
         </is>
       </c>
-      <c r="H7" s="49" t="inlineStr">
+      <c r="H7" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16032,7 +16510,7 @@
           <t>Jewelry</t>
         </is>
       </c>
-      <c r="B8" s="50" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16042,7 +16520,7 @@
           <t>Evening outfits</t>
         </is>
       </c>
-      <c r="D8" s="50" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16052,7 +16530,7 @@
           <t>Band-aids</t>
         </is>
       </c>
-      <c r="F8" s="50" t="inlineStr">
+      <c r="F8" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16062,7 +16540,7 @@
           <t>Cake server set</t>
         </is>
       </c>
-      <c r="H8" s="50" t="inlineStr">
+      <c r="H8" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16074,7 +16552,7 @@
           <t>Vows book</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16084,7 +16562,7 @@
           <t>Sunscreen</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16094,7 +16572,7 @@
           <t>Pain reliever</t>
         </is>
       </c>
-      <c r="F9" s="49" t="inlineStr">
+      <c r="F9" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16104,7 +16582,7 @@
           <t>Table numbers</t>
         </is>
       </c>
-      <c r="H9" s="49" t="inlineStr">
+      <c r="H9" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16116,7 +16594,7 @@
           <t>Rings</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16126,7 +16604,7 @@
           <t>Adapters</t>
         </is>
       </c>
-      <c r="D10" s="50" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16136,7 +16614,7 @@
           <t>Bobby pins</t>
         </is>
       </c>
-      <c r="F10" s="50" t="inlineStr">
+      <c r="F10" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16146,7 +16624,7 @@
           <t>Place cards</t>
         </is>
       </c>
-      <c r="H10" s="50" t="inlineStr">
+      <c r="H10" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16158,7 +16636,7 @@
           <t>Something blue</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16168,7 +16646,7 @@
           <t>Medications</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16178,7 +16656,7 @@
           <t>Mints</t>
         </is>
       </c>
-      <c r="F11" s="49" t="inlineStr">
+      <c r="F11" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16188,7 +16666,7 @@
           <t>Signage</t>
         </is>
       </c>
-      <c r="H11" s="49" t="inlineStr">
+      <c r="H11" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16200,7 +16678,7 @@
           <t>Emergency kit</t>
         </is>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16210,7 +16688,7 @@
           <t>Camera</t>
         </is>
       </c>
-      <c r="D12" s="50" t="inlineStr">
+      <c r="D12" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16220,7 +16698,7 @@
           <t>Tissues</t>
         </is>
       </c>
-      <c r="F12" s="50" t="inlineStr">
+      <c r="F12" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16230,7 +16708,7 @@
           <t>Favors</t>
         </is>
       </c>
-      <c r="H12" s="50" t="inlineStr">
+      <c r="H12" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16242,7 +16720,7 @@
           <t>Robe for getting ready</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16252,7 +16730,7 @@
           <t>Chargers</t>
         </is>
       </c>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16262,7 +16740,7 @@
           <t>Deodorant</t>
         </is>
       </c>
-      <c r="F13" s="49" t="inlineStr">
+      <c r="F13" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16272,7 +16750,7 @@
           <t>Tip envelopes</t>
         </is>
       </c>
-      <c r="H13" s="49" t="inlineStr">
+      <c r="H13" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16284,7 +16762,7 @@
           <t>Perfume</t>
         </is>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16294,7 +16772,7 @@
           <t>Travel insurance docs</t>
         </is>
       </c>
-      <c r="D14" s="50" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16304,7 +16782,7 @@
           <t>Phone charger</t>
         </is>
       </c>
-      <c r="F14" s="50" t="inlineStr">
+      <c r="F14" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16314,7 +16792,7 @@
           <t>Timeline printouts</t>
         </is>
       </c>
-      <c r="H14" s="50" t="inlineStr">
+      <c r="H14" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16326,7 +16804,7 @@
           <t>Flat shoes for reception</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16336,7 +16814,7 @@
           <t>Snacks</t>
         </is>
       </c>
-      <c r="F15" s="49" t="inlineStr">
+      <c r="F15" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16346,7 +16824,7 @@
           <t>Vendor meals list</t>
         </is>
       </c>
-      <c r="H15" s="49" t="inlineStr">
+      <c r="H15" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16358,7 +16836,7 @@
           <t>Static spray</t>
         </is>
       </c>
-      <c r="F16" s="50" t="inlineStr">
+      <c r="F16" s="55" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -16370,7 +16848,7 @@
           <t>Double-sided tape</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="F17" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -17997,7 +18475,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
@@ -18024,7 +18502,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>10:30 AM</t>
         </is>
@@ -18051,7 +18529,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
@@ -18074,7 +18552,7 @@
       <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>12:30 PM</t>
         </is>
@@ -18097,7 +18575,7 @@
       <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
@@ -18124,7 +18602,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>1:30 PM</t>
         </is>
@@ -18147,7 +18625,7 @@
       <c r="E10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>2:30 PM</t>
         </is>
@@ -18174,7 +18652,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
@@ -18197,7 +18675,7 @@
       <c r="E12" s="21" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>3:45 PM</t>
         </is>
@@ -18224,34 +18702,34 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="B14" s="53" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>CEREMONY BEGINS</t>
         </is>
       </c>
-      <c r="C14" s="53" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>Officiant</t>
         </is>
       </c>
-      <c r="D14" s="53" t="inlineStr">
+      <c r="D14" s="58" t="inlineStr">
         <is>
           <t>Ceremony Lawn</t>
         </is>
       </c>
-      <c r="E14" s="53" t="inlineStr">
+      <c r="E14" s="58" t="inlineStr">
         <is>
           <t>Processional</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
@@ -18278,7 +18756,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>5:15 PM</t>
         </is>
@@ -18305,7 +18783,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
@@ -18328,7 +18806,7 @@
       <c r="E17" s="18" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>6:30 PM</t>
         </is>
@@ -18355,7 +18833,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="51" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>7:30 PM</t>
         </is>
@@ -18378,7 +18856,7 @@
       <c r="E19" s="18" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
@@ -18405,7 +18883,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>8:15 PM</t>
         </is>
@@ -18432,7 +18910,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>9:30 PM</t>
         </is>
@@ -18455,7 +18933,7 @@
       <c r="E22" s="21" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="A23" s="56" t="inlineStr">
         <is>
           <t>10:30 PM</t>
         </is>
@@ -18482,7 +18960,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
@@ -18660,7 +19138,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="59">
         <f>AVERAGE(C7:C12)</f>
         <v/>
       </c>
@@ -18675,7 +19153,7 @@
         <f>IFERROR(1-MAX(BudTotalActual-TotalBudget,0)/TotalBudget,0)</f>
         <v/>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="60">
         <f>IF(C7&gt;=0.75,"On Track",IF(C7&gt;=0.5,"Watch","Behind"))</f>
         <v/>
       </c>
@@ -18705,11 +19183,11 @@
         <f>IFERROR(COUNTIF(TLDone,"Yes")/MAX(COUNTA(TLTask),1),0)</f>
         <v/>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="60">
         <f>IF(C9&gt;=0.75,"On Track",IF(C9&gt;=0.5,"Watch","Behind"))</f>
         <v/>
       </c>
-      <c r="F9" s="56" t="inlineStr">
+      <c r="F9" s="61" t="inlineStr">
         <is>
           <t>Wedding Readiness Score</t>
         </is>
@@ -18740,7 +19218,7 @@
         <f>IFERROR((COUNTIF(GuestRsvp,"Accepted")+COUNTIF(GuestRsvp,"Declined"))/MAX(COUNTA(GuestName),1),0)</f>
         <v/>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="60">
         <f>IF(C11&gt;=0.75,"On Track",IF(C11&gt;=0.5,"Watch","Behind"))</f>
         <v/>
       </c>
@@ -18860,7 +19338,7 @@
           <t>Wedding Date</t>
         </is>
       </c>
-      <c r="C6" s="57" t="n">
+      <c r="C6" s="62" t="n">
         <v>46550</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
@@ -19090,7 +19568,7 @@
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="C12" s="58" t="n">
+      <c r="C12" s="63" t="n">
         <v>0.08</v>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -19120,7 +19598,7 @@
           <t>Today (auto)</t>
         </is>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="62">
         <f>TODAY()</f>
         <v/>
       </c>
@@ -19180,6 +19658,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Tables (for seating)</t>
+        </is>
+      </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Hair</t>
@@ -19197,6 +19680,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Makeup</t>
@@ -19209,6 +19697,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Invitations</t>
@@ -19221,6 +19714,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Table 3</t>
+        </is>
+      </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Transportation</t>
@@ -19233,6 +19731,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Accommodation</t>
@@ -19245,6 +19748,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Table 5</t>
+        </is>
+      </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
           <t>Entertainment</t>
@@ -19257,6 +19765,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Table 6</t>
+        </is>
+      </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
           <t>Music</t>
@@ -19269,6 +19782,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Table 7</t>
+        </is>
+      </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
           <t>Catering</t>
@@ -19276,6 +19794,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Table 8</t>
+        </is>
+      </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
           <t>Bar</t>
@@ -19283,6 +19806,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Table 9</t>
+        </is>
+      </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Flowers</t>
@@ -19290,6 +19818,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Table 10</t>
+        </is>
+      </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
           <t>RSVP Status</t>
@@ -19322,6 +19855,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Table 11</t>
+        </is>
+      </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -19354,6 +19892,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Table 12</t>
+        </is>
+      </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
           <t>Accepted</t>
@@ -19386,6 +19929,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Table 13</t>
+        </is>
+      </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Declined</t>
@@ -19413,6 +19961,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Table 14</t>
+        </is>
+      </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Not Started</t>
@@ -19435,6 +19988,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Table 15</t>
+        </is>
+      </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
           <t>PayPal</t>
@@ -19452,6 +20010,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Table 16</t>
+        </is>
+      </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
           <t>Venmo</t>
@@ -19469,6 +20032,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Table 17</t>
+        </is>
+      </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
           <t>2 Weeks</t>
@@ -19476,6 +20044,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Table 18</t>
+        </is>
+      </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
           <t>Wedding Week</t>
@@ -19483,6 +20056,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Table 19</t>
+        </is>
+      </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
           <t>Wedding Day</t>
@@ -19490,6 +20068,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Table 20</t>
+        </is>
+      </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
           <t>Post Wedding</t>
